--- a/docs/downloads/05/tbl_comfort_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_comfort_alaotra_tous.xlsx
@@ -383,10 +383,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>564.5</v>
       </c>
     </row>
     <row r="3">
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>202</v>
+        <v>436</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>641.2</v>
       </c>
     </row>
     <row r="4">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>171</v>
+        <v>361</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>622.4</v>
       </c>
     </row>
     <row r="5">
@@ -422,10 +422,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>140</v>
+        <v>297</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>571.2</v>
       </c>
     </row>
     <row r="6">
@@ -435,10 +435,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>129</v>
+        <v>263</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>571.7</v>
       </c>
     </row>
     <row r="7">
@@ -448,10 +448,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>242</v>
+        <v>544</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>604.4</v>
       </c>
     </row>
     <row r="8">
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>265</v>
+        <v>547</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>614.6</v>
       </c>
     </row>
     <row r="9">
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>185</v>
+        <v>433</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>593.2</v>
       </c>
     </row>
     <row r="10">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>1428</v>
+        <v>3056</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>602.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_comfort_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_comfort_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="C2">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="C3">
@@ -405,7 +405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="C4">
@@ -418,7 +418,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="C5">
@@ -431,7 +431,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="C6">
@@ -444,7 +444,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="C7">
@@ -457,7 +457,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="C8">
@@ -470,7 +470,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="C9">
@@ -483,7 +483,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="C10">
